--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/69.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/69.xlsx
@@ -426,13 +426,13 @@
         <v>-3.830669268188851</v>
       </c>
       <c r="E2">
-        <v>-7.894762522719796</v>
+        <v>-8.502125985102552</v>
       </c>
       <c r="F2">
-        <v>-3.735743295901023</v>
+        <v>-4.142053365137166</v>
       </c>
       <c r="G2">
-        <v>-7.485459116786719</v>
+        <v>-8.596107418665731</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.729031949112577</v>
       </c>
       <c r="E3">
-        <v>-7.023986784258871</v>
+        <v>-8.941365321476539</v>
       </c>
       <c r="F3">
-        <v>-3.810446296652885</v>
+        <v>-3.911551851634176</v>
       </c>
       <c r="G3">
-        <v>-7.352183174466739</v>
+        <v>-8.397815672500004</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.77460120432037</v>
       </c>
       <c r="E4">
-        <v>-7.856777682743457</v>
+        <v>-9.863131677263832</v>
       </c>
       <c r="F4">
-        <v>-3.476624173733518</v>
+        <v>-3.667077436780763</v>
       </c>
       <c r="G4">
-        <v>-6.972500017113266</v>
+        <v>-8.149577725783294</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.954316104744655</v>
       </c>
       <c r="E5">
-        <v>-9.648110674431628</v>
+        <v>-8.754842005574604</v>
       </c>
       <c r="F5">
-        <v>-3.998020154608</v>
+        <v>-3.895678675461732</v>
       </c>
       <c r="G5">
-        <v>-6.676785536817867</v>
+        <v>-8.016258746371303</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.219898940694295</v>
       </c>
       <c r="E6">
-        <v>-10.27787196925632</v>
+        <v>-10.74021105154343</v>
       </c>
       <c r="F6">
-        <v>-3.659234454211058</v>
+        <v>-3.724251354921985</v>
       </c>
       <c r="G6">
-        <v>-6.290206513106092</v>
+        <v>-7.357347625508003</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.521964538076405</v>
       </c>
       <c r="E7">
-        <v>-9.661125508729674</v>
+        <v>-10.85062883327246</v>
       </c>
       <c r="F7">
-        <v>-3.557061133647558</v>
+        <v>-3.543248935573279</v>
       </c>
       <c r="G7">
-        <v>-6.701829813822454</v>
+        <v>-7.655376177135351</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.807665149096703</v>
       </c>
       <c r="E8">
-        <v>-10.94018393524815</v>
+        <v>-12.52491888575838</v>
       </c>
       <c r="F8">
-        <v>-3.399592632212387</v>
+        <v>-3.529102905435672</v>
       </c>
       <c r="G8">
-        <v>-6.135610657513206</v>
+        <v>-7.621456327539979</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.026176365078963</v>
       </c>
       <c r="E9">
-        <v>-11.20044439341698</v>
+        <v>-11.04873145721201</v>
       </c>
       <c r="F9">
-        <v>-3.466377268960888</v>
+        <v>-3.373003695317328</v>
       </c>
       <c r="G9">
-        <v>-6.376886526960829</v>
+        <v>-8.112363883376347</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.136217940838421</v>
       </c>
       <c r="E10">
-        <v>-11.18195010556965</v>
+        <v>-12.57907490641611</v>
       </c>
       <c r="F10">
-        <v>-3.276506348197811</v>
+        <v>-3.263657541412988</v>
       </c>
       <c r="G10">
-        <v>-6.637899868913588</v>
+        <v>-7.441991653856088</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.116603859655769</v>
       </c>
       <c r="E11">
-        <v>-12.59212144003221</v>
+        <v>-13.00097471581473</v>
       </c>
       <c r="F11">
-        <v>-3.093787551590504</v>
+        <v>-3.237957442741133</v>
       </c>
       <c r="G11">
-        <v>-6.536269431403501</v>
+        <v>-7.515032220089028</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.96330379094889</v>
       </c>
       <c r="E12">
-        <v>-12.96473333833134</v>
+        <v>-12.81189281209846</v>
       </c>
       <c r="F12">
-        <v>-2.982667034709367</v>
+        <v>-2.777583146593877</v>
       </c>
       <c r="G12">
-        <v>-6.358996338866608</v>
+        <v>-7.248715384182358</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.691147890013174</v>
       </c>
       <c r="E13">
-        <v>-13.49422969015221</v>
+        <v>-14.3600875058408</v>
       </c>
       <c r="F13">
-        <v>-2.7788033317782</v>
+        <v>-2.654820754233796</v>
       </c>
       <c r="G13">
-        <v>-5.799398273635903</v>
+        <v>-6.704743093897013</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.33862846127022</v>
       </c>
       <c r="E14">
-        <v>-13.69186588126897</v>
+        <v>-14.84321228382312</v>
       </c>
       <c r="F14">
-        <v>-2.487413500699835</v>
+        <v>-2.730961800796918</v>
       </c>
       <c r="G14">
-        <v>-6.07436225449115</v>
+        <v>-6.700585048699688</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.955103453371718</v>
       </c>
       <c r="E15">
-        <v>-15.06273006134494</v>
+        <v>-15.63167395024663</v>
       </c>
       <c r="F15">
-        <v>-2.062166952635695</v>
+        <v>-2.145566982749549</v>
       </c>
       <c r="G15">
-        <v>-5.369497450997225</v>
+        <v>-6.627014795180465</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.59181775935118</v>
       </c>
       <c r="E16">
-        <v>-15.30813259629461</v>
+        <v>-16.34190622818762</v>
       </c>
       <c r="F16">
-        <v>-1.930445766814337</v>
+        <v>-2.304117332012777</v>
       </c>
       <c r="G16">
-        <v>-5.619946842134169</v>
+        <v>-6.438618269631619</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.296947854005016</v>
       </c>
       <c r="E17">
-        <v>-16.09686144268456</v>
+        <v>-17.44322657837904</v>
       </c>
       <c r="F17">
-        <v>-1.73147025992709</v>
+        <v>-1.717933908197944</v>
       </c>
       <c r="G17">
-        <v>-5.086171032109779</v>
+        <v>-6.079523394986873</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.108246678253065</v>
       </c>
       <c r="E18">
-        <v>-17.60163259916735</v>
+        <v>-17.31115363394534</v>
       </c>
       <c r="F18">
-        <v>-1.360039428553223</v>
+        <v>-1.184310396090739</v>
       </c>
       <c r="G18">
-        <v>-5.355467359001794</v>
+        <v>-6.020645342570936</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.044388485665116</v>
       </c>
       <c r="E19">
-        <v>-17.88453089890053</v>
+        <v>-18.96322246447562</v>
       </c>
       <c r="F19">
-        <v>-0.8297790881013837</v>
+        <v>-1.198677600324893</v>
       </c>
       <c r="G19">
-        <v>-4.132339961880504</v>
+        <v>-5.573840874408739</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.103778609827186</v>
       </c>
       <c r="E20">
-        <v>-19.31426524107622</v>
+        <v>-19.38072059713878</v>
       </c>
       <c r="F20">
-        <v>-0.7452657321981669</v>
+        <v>-0.7635552560845772</v>
       </c>
       <c r="G20">
-        <v>-4.621595555492775</v>
+        <v>-5.430080434365888</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.275292122739752</v>
       </c>
       <c r="E21">
-        <v>-19.68987951764244</v>
+        <v>-19.43620346068076</v>
       </c>
       <c r="F21">
-        <v>-0.5152065668882715</v>
+        <v>-0.4527186718580908</v>
       </c>
       <c r="G21">
-        <v>-4.216785357496233</v>
+        <v>-5.40718139087075</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.533405059213016</v>
       </c>
       <c r="E22">
-        <v>-20.10381826973557</v>
+        <v>-21.42896297623011</v>
       </c>
       <c r="F22">
-        <v>-0.08228188136758265</v>
+        <v>-0.3875675756279097</v>
       </c>
       <c r="G22">
-        <v>-5.117402718727264</v>
+        <v>-4.924556819973638</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.844043332199158</v>
       </c>
       <c r="E23">
-        <v>-21.50125553528856</v>
+        <v>-21.38618248227965</v>
       </c>
       <c r="F23">
-        <v>0.007712781639958445</v>
+        <v>-0.1684420316675648</v>
       </c>
       <c r="G23">
-        <v>-4.265165670007143</v>
+        <v>-5.126337881137757</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.179198780145203</v>
       </c>
       <c r="E24">
-        <v>-20.35714563419866</v>
+        <v>-22.29182747059964</v>
       </c>
       <c r="F24">
-        <v>0.1682744069571838</v>
+        <v>0.04338476710671355</v>
       </c>
       <c r="G24">
-        <v>-4.638280705010702</v>
+        <v>-5.294467246895183</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.512602147017879</v>
       </c>
       <c r="E25">
-        <v>-22.14121948205253</v>
+        <v>-21.98693437261121</v>
       </c>
       <c r="F25">
-        <v>0.08606308406634688</v>
+        <v>-0.004428599382873909</v>
       </c>
       <c r="G25">
-        <v>-4.148945658305489</v>
+        <v>-5.153255926917571</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.820487097791784</v>
       </c>
       <c r="E26">
-        <v>-21.7356629353476</v>
+        <v>-22.43247281632986</v>
       </c>
       <c r="F26">
-        <v>0.02736579827137672</v>
+        <v>-0.3580727258838304</v>
       </c>
       <c r="G26">
-        <v>-4.798752778935794</v>
+        <v>-5.224091669821356</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.084903604919937</v>
       </c>
       <c r="E27">
-        <v>-22.30312148477476</v>
+        <v>-23.04116312159686</v>
       </c>
       <c r="F27">
-        <v>0.04764506065931141</v>
+        <v>-0.2100103363074468</v>
       </c>
       <c r="G27">
-        <v>-5.087220475045728</v>
+        <v>-5.30924552218249</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.293459475758987</v>
       </c>
       <c r="E28">
-        <v>-22.34805753235288</v>
+        <v>-22.93950793707268</v>
       </c>
       <c r="F28">
-        <v>0.05886861059984191</v>
+        <v>-0.1191492009965774</v>
       </c>
       <c r="G28">
-        <v>-4.795611071219025</v>
+        <v>-5.55475888992038</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.434508394495738</v>
       </c>
       <c r="E29">
-        <v>-21.87950991220125</v>
+        <v>-22.51507218222977</v>
       </c>
       <c r="F29">
-        <v>0.04512516701999532</v>
+        <v>-0.2802517502278309</v>
       </c>
       <c r="G29">
-        <v>-5.020218343876419</v>
+        <v>-5.919342649069238</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.497568477119064</v>
       </c>
       <c r="E30">
-        <v>-22.0130863100055</v>
+        <v>-22.99503155688073</v>
       </c>
       <c r="F30">
-        <v>-0.09862060002040009</v>
+        <v>-0.4514231052401123</v>
       </c>
       <c r="G30">
-        <v>-5.56407145452235</v>
+        <v>-5.994157667711227</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.477982984723635</v>
       </c>
       <c r="E31">
-        <v>-21.99613623179479</v>
+        <v>-23.0769018384654</v>
       </c>
       <c r="F31">
-        <v>-0.09653891273716493</v>
+        <v>-0.5924178641358105</v>
       </c>
       <c r="G31">
-        <v>-5.104312821664985</v>
+        <v>-5.788158971530077</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.371205028013422</v>
       </c>
       <c r="E32">
-        <v>-22.10923939861037</v>
+        <v>-22.30421737548462</v>
       </c>
       <c r="F32">
-        <v>-0.1943956107646761</v>
+        <v>-0.4919360698088278</v>
       </c>
       <c r="G32">
-        <v>-4.964554831179113</v>
+        <v>-5.769487494688588</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.173786114620154</v>
       </c>
       <c r="E33">
-        <v>-21.62140953613408</v>
+        <v>-21.41056831481095</v>
       </c>
       <c r="F33">
-        <v>-0.8830994410847823</v>
+        <v>-0.5583114930603466</v>
       </c>
       <c r="G33">
-        <v>-4.825965463268603</v>
+        <v>-5.469095213546199</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.888083974442119</v>
       </c>
       <c r="E34">
-        <v>-21.83564258448894</v>
+        <v>-22.43258602818005</v>
       </c>
       <c r="F34">
-        <v>-0.5226295671847578</v>
+        <v>-0.9075843247767301</v>
       </c>
       <c r="G34">
-        <v>-4.979932315209028</v>
+        <v>-5.498098903015753</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.521137539463344</v>
       </c>
       <c r="E35">
-        <v>-21.01649597818947</v>
+        <v>-22.62716097086762</v>
       </c>
       <c r="F35">
-        <v>-0.2355729259904367</v>
+        <v>-0.901416301095485</v>
       </c>
       <c r="G35">
-        <v>-5.118713694760815</v>
+        <v>-5.121468068649489</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.083458091445771</v>
       </c>
       <c r="E36">
-        <v>-21.416500615761</v>
+        <v>-21.87316099164249</v>
       </c>
       <c r="F36">
-        <v>-0.9288775088656914</v>
+        <v>-0.9978366100465418</v>
       </c>
       <c r="G36">
-        <v>-4.108560313271919</v>
+        <v>-5.389542804237513</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.589960818662343</v>
       </c>
       <c r="E37">
-        <v>-20.82726010635694</v>
+        <v>-21.16297852691558</v>
       </c>
       <c r="F37">
-        <v>-0.6924001529189053</v>
+        <v>-1.152717291715368</v>
       </c>
       <c r="G37">
-        <v>-4.380521629323047</v>
+        <v>-4.481096002806106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.060960179415161</v>
       </c>
       <c r="E38">
-        <v>-19.51836356460192</v>
+        <v>-21.32746175982219</v>
       </c>
       <c r="F38">
-        <v>-0.8414632103178707</v>
+        <v>-1.038382709311369</v>
       </c>
       <c r="G38">
-        <v>-3.736203393196853</v>
+        <v>-4.477434539439672</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.518658199441971</v>
       </c>
       <c r="E39">
-        <v>-19.21539959654076</v>
+        <v>-20.58603282444235</v>
       </c>
       <c r="F39">
-        <v>-1.054928519814887</v>
+        <v>-1.106671661263355</v>
       </c>
       <c r="G39">
-        <v>-3.750587713564987</v>
+        <v>-4.012458486812416</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.986102593017285</v>
       </c>
       <c r="E40">
-        <v>-19.37449847385225</v>
+        <v>-20.53284136874825</v>
       </c>
       <c r="F40">
-        <v>-1.119908972360091</v>
+        <v>-1.162192158068589</v>
       </c>
       <c r="G40">
-        <v>-3.706315788068313</v>
+        <v>-4.353537372632448</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.492082928764709</v>
       </c>
       <c r="E41">
-        <v>-18.6579761455146</v>
+        <v>-19.46846883798541</v>
       </c>
       <c r="F41">
-        <v>-1.155657995995306</v>
+        <v>-1.285095372887146</v>
       </c>
       <c r="G41">
-        <v>-3.36701135465733</v>
+        <v>-3.533101424362566</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.0626161081502</v>
       </c>
       <c r="E42">
-        <v>-19.07056088387943</v>
+        <v>-19.11329156461581</v>
       </c>
       <c r="F42">
-        <v>-1.360665674309739</v>
+        <v>-1.036106355688476</v>
       </c>
       <c r="G42">
-        <v>-3.112609172146497</v>
+        <v>-3.613680102788427</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.714242578460679</v>
       </c>
       <c r="E43">
-        <v>-17.63275227254806</v>
+        <v>-20.14763125575978</v>
       </c>
       <c r="F43">
-        <v>-1.41980116646079</v>
+        <v>-1.291864791302824</v>
       </c>
       <c r="G43">
-        <v>-3.178886293842706</v>
+        <v>-4.02811074612209</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.4547815630633483</v>
       </c>
       <c r="E44">
-        <v>-17.83908313375955</v>
+        <v>-18.77333902086</v>
       </c>
       <c r="F44">
-        <v>-1.709310603534801</v>
+        <v>-1.593388869187038</v>
       </c>
       <c r="G44">
-        <v>-3.265506717877737</v>
+        <v>-3.234430626900598</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.2822100638902173</v>
       </c>
       <c r="E45">
-        <v>-17.94800651906604</v>
+        <v>-19.31337766017072</v>
       </c>
       <c r="F45">
-        <v>-1.436331237983655</v>
+        <v>-1.500469240880212</v>
       </c>
       <c r="G45">
-        <v>-3.017993780634126</v>
+        <v>-3.773029901775706</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.185556176883949</v>
       </c>
       <c r="E46">
-        <v>-17.45037251036315</v>
+        <v>-18.66608664246233</v>
       </c>
       <c r="F46">
-        <v>-1.677058947074205</v>
+        <v>-1.559916199174715</v>
       </c>
       <c r="G46">
-        <v>-3.515072193355695</v>
+        <v>-3.553169951421628</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.147532893730752</v>
       </c>
       <c r="E47">
-        <v>-16.9256084138803</v>
+        <v>-18.38508124486436</v>
       </c>
       <c r="F47">
-        <v>-1.8037312335755</v>
+        <v>-1.874704095912556</v>
       </c>
       <c r="G47">
-        <v>-3.469555502736255</v>
+        <v>-3.564005366971662</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.1492520253883243</v>
       </c>
       <c r="E48">
-        <v>-17.24334879262849</v>
+        <v>-17.70713245812405</v>
       </c>
       <c r="F48">
-        <v>-2.078583537824376</v>
+        <v>-1.572285381233318</v>
       </c>
       <c r="G48">
-        <v>-3.198256295792981</v>
+        <v>-3.02451886589203</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.1702018910748065</v>
       </c>
       <c r="E49">
-        <v>-16.79774695027373</v>
+        <v>-17.74012239126993</v>
       </c>
       <c r="F49">
-        <v>-2.139306181919191</v>
+        <v>-1.710657528931753</v>
       </c>
       <c r="G49">
-        <v>-3.087144455858423</v>
+        <v>-3.651850692856223</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.1912064607703221</v>
       </c>
       <c r="E50">
-        <v>-15.99095854954118</v>
+        <v>-17.1687874680922</v>
       </c>
       <c r="F50">
-        <v>-2.292935200442387</v>
+        <v>-1.869468813926863</v>
       </c>
       <c r="G50">
-        <v>-3.202745395544233</v>
+        <v>-3.566296264484838</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.1988194110667493</v>
       </c>
       <c r="E51">
-        <v>-16.31954009506374</v>
+        <v>-16.90957761589315</v>
       </c>
       <c r="F51">
-        <v>-2.204091139757334</v>
+        <v>-1.960242970660438</v>
       </c>
       <c r="G51">
-        <v>-3.866910352178358</v>
+        <v>-3.351157152069761</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.1844016921616802</v>
       </c>
       <c r="E52">
-        <v>-15.50995309739445</v>
+        <v>-16.40771401246709</v>
       </c>
       <c r="F52">
-        <v>-2.322121897512625</v>
+        <v>-2.263641643977188</v>
       </c>
       <c r="G52">
-        <v>-3.260521036295594</v>
+        <v>-3.291494500361015</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1456567293100304</v>
       </c>
       <c r="E53">
-        <v>-15.565182366392</v>
+        <v>-15.94904752260019</v>
       </c>
       <c r="F53">
-        <v>-2.441507864338895</v>
+        <v>-2.160252280066379</v>
       </c>
       <c r="G53">
-        <v>-3.416497389378356</v>
+        <v>-3.578945858990393</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.08855452085300596</v>
       </c>
       <c r="E54">
-        <v>-15.69476465012149</v>
+        <v>-15.86191968269262</v>
       </c>
       <c r="F54">
-        <v>-2.395764587988904</v>
+        <v>-1.73295552268031</v>
       </c>
       <c r="G54">
-        <v>-3.496251741964938</v>
+        <v>-3.886293596310791</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.02586672301894948</v>
       </c>
       <c r="E55">
-        <v>-14.71622481570003</v>
+        <v>-16.11932267376261</v>
       </c>
       <c r="F55">
-        <v>-2.329688205369795</v>
+        <v>-2.224807780133947</v>
       </c>
       <c r="G55">
-        <v>-3.713847279170155</v>
+        <v>-3.910083176555994</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.02624181415690738</v>
       </c>
       <c r="E56">
-        <v>-14.6804272286694</v>
+        <v>-15.52471592265946</v>
       </c>
       <c r="F56">
-        <v>-2.588665676711422</v>
+        <v>-2.178828419074158</v>
       </c>
       <c r="G56">
-        <v>-3.625796699462159</v>
+        <v>-3.692964357908432</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.05107946920264154</v>
       </c>
       <c r="E57">
-        <v>-14.86320096809298</v>
+        <v>-14.88087107367091</v>
       </c>
       <c r="F57">
-        <v>-2.829146532315938</v>
+        <v>-2.227398085002501</v>
       </c>
       <c r="G57">
-        <v>-3.333842998899372</v>
+        <v>-3.866883867814044</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.03134737558959749</v>
       </c>
       <c r="E58">
-        <v>-14.11829869314926</v>
+        <v>-14.77996308735799</v>
       </c>
       <c r="F58">
-        <v>-2.265412693484373</v>
+        <v>-2.319677385306963</v>
       </c>
       <c r="G58">
-        <v>-3.748902645885497</v>
+        <v>-3.687088139576226</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.04590458316451374</v>
       </c>
       <c r="E59">
-        <v>-13.51440404185638</v>
+        <v>-14.71771468364856</v>
       </c>
       <c r="F59">
-        <v>-2.680307962483131</v>
+        <v>-2.232199302469127</v>
       </c>
       <c r="G59">
-        <v>-3.834801370992967</v>
+        <v>-4.39727298975176</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.1866506526780834</v>
       </c>
       <c r="E60">
-        <v>-13.79307274686639</v>
+        <v>-14.89282624505116</v>
       </c>
       <c r="F60">
-        <v>-2.502242933944752</v>
+        <v>-2.446443277324775</v>
       </c>
       <c r="G60">
-        <v>-4.012561113724133</v>
+        <v>-4.647556853611739</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.3900047365348281</v>
       </c>
       <c r="E61">
-        <v>-13.56056730589057</v>
+        <v>-14.31140641025835</v>
       </c>
       <c r="F61">
-        <v>-2.398335840407193</v>
+        <v>-2.186477563671609</v>
       </c>
       <c r="G61">
-        <v>-3.913046114813641</v>
+        <v>-4.452926570812448</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.6464342691383576</v>
       </c>
       <c r="E62">
-        <v>-14.29564279223765</v>
+        <v>-14.39065923386659</v>
       </c>
       <c r="F62">
-        <v>-2.6374233820402</v>
+        <v>-2.114309367172313</v>
       </c>
       <c r="G62">
-        <v>-4.240862955203353</v>
+        <v>-4.752749438122081</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.9398121705716412</v>
       </c>
       <c r="E63">
-        <v>-13.58016201292176</v>
+        <v>-14.43585340446314</v>
       </c>
       <c r="F63">
-        <v>-2.452551658553018</v>
+        <v>-2.270398636881823</v>
       </c>
       <c r="G63">
-        <v>-4.109920947488559</v>
+        <v>-4.483555738141784</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.251066924731368</v>
       </c>
       <c r="E64">
-        <v>-12.9778160997395</v>
+        <v>-14.4915038215434</v>
       </c>
       <c r="F64">
-        <v>-2.721439717501738</v>
+        <v>-2.271574918593799</v>
       </c>
       <c r="G64">
-        <v>-4.125394437339113</v>
+        <v>-4.894503687568134</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.560836568075849</v>
       </c>
       <c r="E65">
-        <v>-13.27064987144551</v>
+        <v>-13.34050158301382</v>
       </c>
       <c r="F65">
-        <v>-2.796294309488312</v>
+        <v>-2.451103672332925</v>
       </c>
       <c r="G65">
-        <v>-3.816368253430305</v>
+        <v>-4.830630021933437</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.850113514161657</v>
       </c>
       <c r="E66">
-        <v>-12.48103797262406</v>
+        <v>-13.29861319844287</v>
       </c>
       <c r="F66">
-        <v>-3.09569776682136</v>
+        <v>-2.477252746137097</v>
       </c>
       <c r="G66">
-        <v>-4.081152306752293</v>
+        <v>-4.799630073503701</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.102467086057531</v>
       </c>
       <c r="E67">
-        <v>-12.65450116948787</v>
+        <v>-13.1217491175993</v>
       </c>
       <c r="F67">
-        <v>-2.926510351738783</v>
+        <v>-2.472500402347236</v>
       </c>
       <c r="G67">
-        <v>-4.534137563436309</v>
+        <v>-5.225899227685798</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.308207327526137</v>
       </c>
       <c r="E68">
-        <v>-13.31580328577599</v>
+        <v>-13.38114916570667</v>
       </c>
       <c r="F68">
-        <v>-3.113245073514862</v>
+        <v>-2.52254373388516</v>
       </c>
       <c r="G68">
-        <v>-3.90564704553337</v>
+        <v>-5.22648188370071</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.461767941924439</v>
       </c>
       <c r="E69">
-        <v>-13.03740628920644</v>
+        <v>-13.39860643300624</v>
       </c>
       <c r="F69">
-        <v>-3.048204150149253</v>
+        <v>-2.516675579203728</v>
       </c>
       <c r="G69">
-        <v>-4.45268490098808</v>
+        <v>-5.069840110964554</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.562194197210187</v>
       </c>
       <c r="E70">
-        <v>-12.60102441993129</v>
+        <v>-13.20577948128563</v>
       </c>
       <c r="F70">
-        <v>-2.828328105321972</v>
+        <v>-2.434039303835255</v>
       </c>
       <c r="G70">
-        <v>-4.342751615265502</v>
+        <v>-4.837098827917172</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.614124663501749</v>
       </c>
       <c r="E71">
-        <v>-13.15028303232163</v>
+        <v>-13.52595165057594</v>
       </c>
       <c r="F71">
-        <v>-3.027247283225828</v>
+        <v>-2.773076827922647</v>
       </c>
       <c r="G71">
-        <v>-4.744741228462584</v>
+        <v>-5.179548279590462</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.626019420822682</v>
       </c>
       <c r="E72">
-        <v>-12.98464051006906</v>
+        <v>-13.98796921120851</v>
       </c>
       <c r="F72">
-        <v>-3.072723825272118</v>
+        <v>-2.554755628710421</v>
       </c>
       <c r="G72">
-        <v>-4.302012041859231</v>
+        <v>-4.682678431237868</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.607477152124274</v>
       </c>
       <c r="E73">
-        <v>-12.68203881992851</v>
+        <v>-12.89902065200604</v>
       </c>
       <c r="F73">
-        <v>-3.024678515909747</v>
+        <v>-2.513695113288455</v>
       </c>
       <c r="G73">
-        <v>-4.380640808962461</v>
+        <v>-4.956364541514956</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.568653860361236</v>
       </c>
       <c r="E74">
-        <v>-13.26001248600149</v>
+        <v>-14.32180378657996</v>
       </c>
       <c r="F74">
-        <v>-3.247520944406453</v>
+        <v>-2.880121777182011</v>
       </c>
       <c r="G74">
-        <v>-3.855220815879191</v>
+        <v>-4.432599821201322</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.521400993541801</v>
       </c>
       <c r="E75">
-        <v>-12.90056939011666</v>
+        <v>-13.95123423005829</v>
       </c>
       <c r="F75">
-        <v>-3.026751091151551</v>
+        <v>-2.72078365051872</v>
       </c>
       <c r="G75">
-        <v>-3.064298381091912</v>
+        <v>-4.524821688288799</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.475753544064573</v>
       </c>
       <c r="E76">
-        <v>-13.1188599511824</v>
+        <v>-14.50084153494721</v>
       </c>
       <c r="F76">
-        <v>-3.262648589916378</v>
+        <v>-2.674035564509133</v>
       </c>
       <c r="G76">
-        <v>-3.951120699060799</v>
+        <v>-4.555636246168336</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.43849235213012</v>
       </c>
       <c r="E77">
-        <v>-13.43290962361434</v>
+        <v>-14.81366851939708</v>
       </c>
       <c r="F77">
-        <v>-3.101080498204751</v>
+        <v>-2.814675782156433</v>
       </c>
       <c r="G77">
-        <v>-2.688581257294486</v>
+        <v>-4.748790025657113</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.41821199455759</v>
       </c>
       <c r="E78">
-        <v>-14.8203525470324</v>
+        <v>-14.57942414440232</v>
       </c>
       <c r="F78">
-        <v>-3.120281226234241</v>
+        <v>-3.044073910278895</v>
       </c>
       <c r="G78">
-        <v>-2.960069165333498</v>
+        <v>-4.12976766799649</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.42027100412363</v>
       </c>
       <c r="E79">
-        <v>-15.24349315830912</v>
+        <v>-15.69725531082571</v>
       </c>
       <c r="F79">
-        <v>-3.558109846779502</v>
+        <v>-2.894001901383319</v>
       </c>
       <c r="G79">
-        <v>-3.045348818425124</v>
+        <v>-4.034139249549103</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.446082958478221</v>
       </c>
       <c r="E80">
-        <v>-14.78737619930855</v>
+        <v>-15.37938360633129</v>
       </c>
       <c r="F80">
-        <v>-3.742193792866623</v>
+        <v>-3.269046899735601</v>
       </c>
       <c r="G80">
-        <v>-2.357443939728885</v>
+        <v>-3.979571527425296</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.496799910227022</v>
       </c>
       <c r="E81">
-        <v>-15.99943132440954</v>
+        <v>-16.36979257112685</v>
       </c>
       <c r="F81">
-        <v>-3.827018614913292</v>
+        <v>-3.163275979541743</v>
       </c>
       <c r="G81">
-        <v>-2.750359347602826</v>
+        <v>-3.73798777724252</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.572989170041759</v>
       </c>
       <c r="E82">
-        <v>-16.90095540138254</v>
+        <v>-17.64095333897595</v>
       </c>
       <c r="F82">
-        <v>-3.648435028380761</v>
+        <v>-3.240123623499453</v>
       </c>
       <c r="G82">
-        <v>-2.605771271175156</v>
+        <v>-4.160661678968969</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.672989173736261</v>
       </c>
       <c r="E83">
-        <v>-17.2594746885698</v>
+        <v>-17.80962541033965</v>
       </c>
       <c r="F83">
-        <v>-3.791630759465697</v>
+        <v>-3.438301412577804</v>
       </c>
       <c r="G83">
-        <v>-2.476315698407496</v>
+        <v>-3.30877885862155</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.79312596344003</v>
       </c>
       <c r="E84">
-        <v>-18.61159551472803</v>
+        <v>-18.56387898410921</v>
       </c>
       <c r="F84">
-        <v>-3.545806105745722</v>
+        <v>-3.501958962380738</v>
       </c>
       <c r="G84">
-        <v>-2.16850779525714</v>
+        <v>-3.278510540755994</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.932446569589618</v>
       </c>
       <c r="E85">
-        <v>-19.39103193245425</v>
+        <v>-19.27087793160873</v>
       </c>
       <c r="F85">
-        <v>-3.710002607226431</v>
+        <v>-3.541581431991444</v>
       </c>
       <c r="G85">
-        <v>-2.514145302284748</v>
+        <v>-3.588745073786636</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.086236213879023</v>
       </c>
       <c r="E86">
-        <v>-19.84438652231015</v>
+        <v>-20.70982318991603</v>
       </c>
       <c r="F86">
-        <v>-4.092709175687205</v>
+        <v>-3.448945105336375</v>
       </c>
       <c r="G86">
-        <v>-2.010876169404742</v>
+        <v>-3.503786543612319</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.246003541348575</v>
       </c>
       <c r="E87">
-        <v>-21.63401680777143</v>
+        <v>-21.62348357722959</v>
       </c>
       <c r="F87">
-        <v>-3.958107756406314</v>
+        <v>-3.639384286137773</v>
       </c>
       <c r="G87">
-        <v>-2.276703044571601</v>
+        <v>-3.567292738692159</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.406534658308429</v>
       </c>
       <c r="E88">
-        <v>-23.37175530957882</v>
+        <v>-23.26296777849256</v>
       </c>
       <c r="F88">
-        <v>-4.076680266443035</v>
+        <v>-3.864934647674231</v>
       </c>
       <c r="G88">
-        <v>-1.708126779838392</v>
+        <v>-3.110162678992975</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.561323032320273</v>
       </c>
       <c r="E89">
-        <v>-24.09524695941428</v>
+        <v>-25.66669989566001</v>
       </c>
       <c r="F89">
-        <v>-3.879192507411216</v>
+        <v>-4.120305407344068</v>
       </c>
       <c r="G89">
-        <v>-2.60430138895572</v>
+        <v>-3.481864111051266</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.703269482780569</v>
       </c>
       <c r="E90">
-        <v>-25.95900383590712</v>
+        <v>-26.14176398990868</v>
       </c>
       <c r="F90">
-        <v>-4.210556864246477</v>
+        <v>-3.71231623738245</v>
       </c>
       <c r="G90">
-        <v>-2.534832901359653</v>
+        <v>-3.480771631023306</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.82901969205487</v>
       </c>
       <c r="E91">
-        <v>-27.84103763349492</v>
+        <v>-29.19184520219093</v>
       </c>
       <c r="F91">
-        <v>-4.217701533095623</v>
+        <v>-3.93902134307841</v>
       </c>
       <c r="G91">
-        <v>-2.269068926558041</v>
+        <v>-3.239111738293127</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.940955687419332</v>
       </c>
       <c r="E92">
-        <v>-29.40591975395553</v>
+        <v>-30.47199046247125</v>
       </c>
       <c r="F92">
-        <v>-4.163340750654308</v>
+        <v>-3.8683872830091</v>
       </c>
       <c r="G92">
-        <v>-2.960161860608598</v>
+        <v>-3.486038708976287</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.042260861561737</v>
       </c>
       <c r="E93">
-        <v>-32.01702654559324</v>
+        <v>-32.19189809787343</v>
       </c>
       <c r="F93">
-        <v>-4.084522420645338</v>
+        <v>-3.83509602545799</v>
       </c>
       <c r="G93">
-        <v>-3.076414977765645</v>
+        <v>-3.52499389833689</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.136287670698741</v>
       </c>
       <c r="E94">
-        <v>-33.65322307472664</v>
+        <v>-33.79847161428566</v>
       </c>
       <c r="F94">
-        <v>-4.157255563713343</v>
+        <v>-4.1945851123531</v>
       </c>
       <c r="G94">
-        <v>-3.352590618288265</v>
+        <v>-4.071290191590804</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.232814699264494</v>
       </c>
       <c r="E95">
-        <v>-35.89741478836687</v>
+        <v>-36.42341968672781</v>
       </c>
       <c r="F95">
-        <v>-4.30924275804419</v>
+        <v>-4.260962192339425</v>
       </c>
       <c r="G95">
-        <v>-3.372361196248792</v>
+        <v>-3.954173022048007</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.337157764872474</v>
       </c>
       <c r="E96">
-        <v>-38.34501423324662</v>
+        <v>-38.23763732181374</v>
       </c>
       <c r="F96">
-        <v>-4.162788229596641</v>
+        <v>-4.228637639547382</v>
       </c>
       <c r="G96">
-        <v>-3.026945495772316</v>
+        <v>-4.424257246442359</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.450550349712183</v>
       </c>
       <c r="E97">
-        <v>-39.85108732600662</v>
+        <v>-40.56664735361764</v>
       </c>
       <c r="F97">
-        <v>-3.964836584819254</v>
+        <v>-4.325097710133774</v>
       </c>
       <c r="G97">
-        <v>-4.004294681512573</v>
+        <v>-4.765375858808862</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.573354892375709</v>
       </c>
       <c r="E98">
-        <v>-42.16335332516715</v>
+        <v>-43.27829306093664</v>
       </c>
       <c r="F98">
-        <v>-4.414637599437177</v>
+        <v>-4.314615549018749</v>
       </c>
       <c r="G98">
-        <v>-4.341685619601857</v>
+        <v>-4.862576786387403</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.702273343082877</v>
       </c>
       <c r="E99">
-        <v>-44.90800028681705</v>
+        <v>-44.62008217364637</v>
       </c>
       <c r="F99">
-        <v>-4.166096729003423</v>
+        <v>-4.197122401707875</v>
       </c>
       <c r="G99">
-        <v>-4.577757311461746</v>
+        <v>-5.353004313120576</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.82326516709444</v>
       </c>
       <c r="E100">
-        <v>-47.828610162983</v>
+        <v>-47.06655402849822</v>
       </c>
       <c r="F100">
-        <v>-4.413488653849495</v>
+        <v>-4.518494162563165</v>
       </c>
       <c r="G100">
-        <v>-5.322908143623062</v>
+        <v>-6.166451699757056</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.921410864612866</v>
       </c>
       <c r="E101">
-        <v>-48.92847121242545</v>
+        <v>-50.01218372355655</v>
       </c>
       <c r="F101">
-        <v>-4.596280346788247</v>
+        <v>-4.355984217114556</v>
       </c>
       <c r="G101">
-        <v>-5.756434013627241</v>
+        <v>-6.981315999884345</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.973390735520619</v>
       </c>
       <c r="E102">
-        <v>-51.40827829656626</v>
+        <v>-52.42283534900772</v>
       </c>
       <c r="F102">
-        <v>-4.448685984794445</v>
+        <v>-4.463787122547481</v>
       </c>
       <c r="G102">
-        <v>-6.338530546342834</v>
+        <v>-6.681718249671381</v>
       </c>
     </row>
   </sheetData>
